--- a/03_김현우_Ensemble/artifacts/results/16_ScoreAware_CalibratedEnsemble/16_scoreaware_balanced_submission.xlsx
+++ b/03_김현우_Ensemble/artifacts/results/16_ScoreAware_CalibratedEnsemble/16_scoreaware_balanced_submission.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,10 +424,15 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>HI_last</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>RUL_pred_seconds</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>RUL_pred_hours</t>
         </is>
@@ -440,9 +445,12 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0.46304706</v>
+      </c>
+      <c r="C2" t="n">
         <v>32034.900390625</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>8.898583441840278</v>
       </c>
     </row>
@@ -453,9 +461,12 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0.5003288</v>
+      </c>
+      <c r="C3" t="n">
         <v>33556.13671875</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>9.321149088541667</v>
       </c>
     </row>
@@ -466,9 +477,12 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0.16482818</v>
+      </c>
+      <c r="C4" t="n">
         <v>6449.32666015625</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>1.791479627821181</v>
       </c>
     </row>
@@ -479,9 +493,12 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>0.448163</v>
+      </c>
+      <c r="C5" t="n">
         <v>14112.5263671875</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>3.920146213107639</v>
       </c>
     </row>
@@ -492,10 +509,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>644.3411865234375</v>
+        <v>0.9438727</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1789836629231771</v>
+        <v>10169.52123883337</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.824867010787048</v>
       </c>
     </row>
     <row r="7">
@@ -505,10 +525,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6000</v>
+        <v>0.410086</v>
       </c>
       <c r="C7" t="n">
-        <v>1.666666666666667</v>
+        <v>10399.87361054762</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.888853780707672</v>
       </c>
     </row>
   </sheetData>
